--- a/deliverables/rail_system_modes.xlsx
+++ b/deliverables/rail_system_modes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bsaue\Documents\Projects\hsr-suspension-dynamics\deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B2C2EC8-9CB4-41D7-B4E5-20B7C06B37D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552B15EA-1C14-4EAD-9F2C-52E951FCCAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{DE2D1501-62B0-4236-B422-1747441C6BB1}"/>
   </bookViews>
